--- a/validation/fixtures/gaze/tobii-mini.xlsx
+++ b/validation/fixtures/gaze/tobii-mini.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,17 +512,6 @@
           <t>RecordingStart</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -540,8 +529,6 @@
       <c r="A3" t="n">
         <v>200000</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>900</v>
       </c>
@@ -576,17 +563,11 @@
       <c r="M3" t="n">
         <v>500</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>208333</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>900</v>
       </c>
@@ -621,17 +602,11 @@
       <c r="M4" t="n">
         <v>500</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>216666</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>900</v>
       </c>
@@ -666,17 +641,11 @@
       <c r="M5" t="n">
         <v>500</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>224999</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>900</v>
       </c>
@@ -711,10 +680,6 @@
       <c r="M6" t="n">
         <v>500</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -730,8 +695,6 @@
           <t>Web Page</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Web Page</t>
@@ -743,56 +706,31 @@
       <c r="H7" t="n">
         <v>1080</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="B8" t="inlineStr"/>
+        <v>1000000</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>taskcheck</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
-        <v>500</v>
-      </c>
-      <c r="E8" t="n">
-        <v>300</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Web Page</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>1920</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Fixation</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>150</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>500</v>
-      </c>
-      <c r="M8" t="n">
-        <v>300</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -800,10 +738,8 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2008333</v>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+        <v>2000000</v>
+      </c>
       <c r="D9" t="n">
         <v>500</v>
       </c>
@@ -838,17 +774,11 @@
       <c r="M9" t="n">
         <v>300</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2016666</v>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+        <v>2008333</v>
+      </c>
       <c r="D10" t="n">
         <v>500</v>
       </c>
@@ -883,17 +813,11 @@
       <c r="M10" t="n">
         <v>300</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2024999</v>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+        <v>2016666</v>
+      </c>
       <c r="D11" t="n">
         <v>500</v>
       </c>
@@ -928,17 +852,11 @@
       <c r="M11" t="n">
         <v>300</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2033332</v>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+        <v>2024999</v>
+      </c>
       <c r="D12" t="n">
         <v>500</v>
       </c>
@@ -973,19 +891,17 @@
       <c r="M12" t="n">
         <v>300</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+        <v>2033332</v>
+      </c>
+      <c r="D13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>300</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Web Page</t>
@@ -999,58 +915,46 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+          <t>Fixation</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>150</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>500</v>
+      </c>
+      <c r="M13" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="B14" t="inlineStr"/>
+        <v>2500000</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MouseEvent</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>900</v>
-      </c>
-      <c r="E14" t="n">
-        <v>444</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Web Page</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>1920</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Fixation</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>100</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>900</v>
-      </c>
-      <c r="M14" t="n">
-        <v>444</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1058,15 +962,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4008333</v>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>900</v>
-      </c>
-      <c r="E15" t="n">
-        <v>444</v>
+        <v>3000000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1081,66 +977,34 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Fixation</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>100</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>900</v>
-      </c>
-      <c r="M15" t="n">
-        <v>444</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+          <t>Unclassified</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4016666</v>
-      </c>
-      <c r="B16" t="inlineStr"/>
+        <v>3000000</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>900</v>
-      </c>
-      <c r="E16" t="n">
-        <v>444</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Web Page</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>1920</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Fixation</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>100</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>900</v>
-      </c>
-      <c r="M16" t="n">
-        <v>444</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1148,10 +1012,8 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4024999</v>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+        <v>4000000</v>
+      </c>
       <c r="D17" t="n">
         <v>900</v>
       </c>
@@ -1186,22 +1048,16 @@
       <c r="M17" t="n">
         <v>444</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+        <v>4008333</v>
+      </c>
       <c r="D18" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E18" t="n">
-        <v>600</v>
+        <v>444</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1220,33 +1076,27 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="M18" t="n">
-        <v>600</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>444</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5508333</v>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+        <v>4016666</v>
+      </c>
       <c r="D19" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E19" t="n">
-        <v>600</v>
+        <v>444</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1265,33 +1115,27 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="M19" t="n">
-        <v>600</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+        <v>444</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5516666</v>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+        <v>4024999</v>
+      </c>
       <c r="D20" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="E20" t="n">
-        <v>600</v>
+        <v>444</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1310,36 +1154,28 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="M20" t="n">
-        <v>600</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+        <v>444</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6000000</v>
+        <v>5000000</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WebStimulusEnd</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Web Page</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
@@ -1347,12 +1183,8 @@
           <t>Web Page</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>1920</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1080</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1363,6 +1195,149 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E22" t="n">
+        <v>600</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Web Page</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1920</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Fixation</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>120</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M22" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5508333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E23" t="n">
+        <v>600</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Web Page</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1920</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Fixation</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>120</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M23" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5516666</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E24" t="n">
+        <v>600</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Web Page</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1920</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Fixation</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>120</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M24" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WebStimulusEnd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Web Page</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Web Page</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1920</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1080</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
